--- a/artfynd/A 24538-2023 artfynd.xlsx
+++ b/artfynd/A 24538-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 24538-2023 artfynd.xlsx
+++ b/artfynd/A 24538-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,67 +675,58 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>111926752</v>
+        <v>112061032</v>
       </c>
       <c r="B2" t="n">
-        <v>96735</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93231</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>1968</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Storberget sydväst (Storberget sydväst), Mpd</t>
+          <t>Storberget sydväst, Storberget sydväst, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>623196</v>
+        <v>623215</v>
       </c>
       <c r="R2" t="n">
-        <v>6933441</v>
+        <v>6933489</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,12 +750,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2023-09-11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2023-09-11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,64 +782,46 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112061114</v>
+        <v>112209570</v>
       </c>
       <c r="B3" t="n">
-        <v>96736</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96231</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>2779</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Hedw.) Schimp.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Storberget sydväst (Storberget sydväst), Mpd</t>
+          <t>Storberget sydväst, Storberget sydväst, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>623191</v>
+        <v>623179</v>
       </c>
       <c r="R3" t="n">
-        <v>6933453</v>
+        <v>6933459</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -875,12 +848,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-09-11</t>
+          <t>2023-09-18</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-09-11</t>
+          <t>2023-09-18</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,6 +874,16 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Sten/berg på land</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Stone/rock on land</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -907,15 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>112061032</v>
+        <v>112209075</v>
       </c>
       <c r="B4" t="n">
-        <v>90800</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -923,26 +911,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1968</v>
+        <v>4361</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bankera violascens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -953,14 +941,14 @@
       <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Storberget sydväst (Storberget sydväst), Mpd</t>
+          <t>Storberget sydväst, Storberget sydväst, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>623215</v>
+        <v>623177</v>
       </c>
       <c r="R4" t="n">
-        <v>6933489</v>
+        <v>6933461</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -987,12 +975,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-09-11</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-09-11</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1019,64 +1007,55 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>112061096</v>
+        <v>112209081</v>
       </c>
       <c r="B5" t="n">
-        <v>96736</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>4361</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Storberget sydväst (Storberget sydväst), Mpd</t>
+          <t>Storberget sydväst, Storberget sydväst, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>623217</v>
+        <v>623225</v>
       </c>
       <c r="R5" t="n">
-        <v>6933479</v>
+        <v>6933502</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1103,12 +1082,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-09-11</t>
+          <t>2023-09-18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-09-11</t>
+          <t>2023-09-18</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,16 +1117,11 @@
         <v>112061235</v>
       </c>
       <c r="B6" t="n">
-        <v>90815</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1181,7 +1155,7 @@
       <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Storberget sydväst (Storberget sydväst), Mpd</t>
+          <t>Storberget sydväst, Storberget sydväst, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
@@ -1257,64 +1231,55 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>112061086</v>
+        <v>112061330</v>
       </c>
       <c r="B7" t="n">
-        <v>96736</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89085</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>4379</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Toppvaxing</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hygrocybe conica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schaeff.) P.Kumm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Storberget sydväst (Storberget sydväst), Mpd</t>
+          <t>Storberget sydväst, Storberget sydväst, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>623193</v>
+        <v>623126</v>
       </c>
       <c r="R7" t="n">
-        <v>6933491</v>
+        <v>6933501</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1373,37 +1338,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>112061062</v>
+        <v>112061132</v>
       </c>
       <c r="B8" t="n">
-        <v>103794</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221144</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1413,23 +1373,23 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Storberget sydväst (Storberget sydväst), Mpd</t>
+          <t>Storberget sydväst, Storberget sydväst, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>623215</v>
+        <v>623214</v>
       </c>
       <c r="R8" t="n">
-        <v>6933489</v>
+        <v>6933467</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1485,63 +1445,62 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>112209081</v>
+        <v>111926752</v>
       </c>
       <c r="B9" t="n">
-        <v>90845</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4361</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Storberget sydväst (Storberget sydväst), Mpd</t>
+          <t>Storberget sydväst, Storberget sydväst, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>623225</v>
+        <v>623196</v>
       </c>
       <c r="R9" t="n">
-        <v>6933502</v>
+        <v>6933441</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1565,12 +1524,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-09-18</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-09-18</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1597,15 +1556,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>112209144</v>
+        <v>112061086</v>
       </c>
       <c r="B10" t="n">
-        <v>96775</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1632,7 +1586,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>36</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1640,17 +1594,21 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Storberget sydväst (Storberget sydväst), Mpd</t>
+          <t>Storberget sydväst, Storberget sydväst, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>623207</v>
+        <v>623193</v>
       </c>
       <c r="R10" t="n">
-        <v>6933474</v>
+        <v>6933491</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1677,22 +1635,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-09-18</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>18:51</t>
+          <t>2023-09-11</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-09-18</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>18:51</t>
+          <t>2023-09-11</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1703,11 +1651,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Barrträd</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1724,51 +1667,59 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>112209570</v>
+        <v>112061096</v>
       </c>
       <c r="B11" t="n">
-        <v>93154</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2779</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Storberget sydväst (Storberget sydväst), Mpd</t>
+          <t>Storberget sydväst, Storberget sydväst, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>623178</v>
+        <v>623217</v>
       </c>
       <c r="R11" t="n">
-        <v>6933460</v>
+        <v>6933479</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1795,22 +1746,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-09-18</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>18:25</t>
+          <t>2023-09-11</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-09-18</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>18:25</t>
+          <t>2023-09-11</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1821,16 +1762,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Sten/berg på land</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Stone/rock on land</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1847,15 +1778,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>112209118</v>
+        <v>112061114</v>
       </c>
       <c r="B12" t="n">
-        <v>96775</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1882,7 +1808,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1890,17 +1816,21 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Storberget sydväst (Storberget sydväst), Mpd</t>
+          <t>Storberget sydväst, Storberget sydväst, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>623208</v>
+        <v>623191</v>
       </c>
       <c r="R12" t="n">
-        <v>6933472</v>
+        <v>6933453</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1927,22 +1857,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-09-18</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>18:39</t>
+          <t>2023-09-11</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-09-18</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>18:39</t>
+          <t>2023-09-11</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1953,11 +1873,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Barrträd</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1974,15 +1889,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>112209136</v>
+        <v>112209105</v>
       </c>
       <c r="B13" t="n">
-        <v>96775</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2009,7 +1919,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2020,14 +1930,14 @@
       <c r="K13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Storberget sydväst (Storberget sydväst), Mpd</t>
+          <t>Storberget sydväst, Storberget sydväst, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>623226</v>
+        <v>623190</v>
       </c>
       <c r="R13" t="n">
-        <v>6933506</v>
+        <v>6933473</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2059,7 +1969,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2069,7 +1979,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2101,15 +2011,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>112209105</v>
+        <v>112209118</v>
       </c>
       <c r="B14" t="n">
-        <v>96775</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2136,7 +2041,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2147,14 +2052,14 @@
       <c r="K14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Storberget sydväst (Storberget sydväst), Mpd</t>
+          <t>Storberget sydväst, Storberget sydväst, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>623190</v>
+        <v>623208</v>
       </c>
       <c r="R14" t="n">
-        <v>6933473</v>
+        <v>6933472</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2186,7 +2091,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>18:39</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2196,7 +2101,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>18:39</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2228,60 +2133,55 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>112209075</v>
+        <v>112209136</v>
       </c>
       <c r="B15" t="n">
-        <v>91597</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4361</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Storberget sydväst (Storberget sydväst), Mpd</t>
+          <t>Storberget sydväst, Storberget sydväst, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>623177</v>
+        <v>623226</v>
       </c>
       <c r="R15" t="n">
-        <v>6933461</v>
+        <v>6933506</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2308,12 +2208,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2023-09-18</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>19:15</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2023-09-18</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>19:15</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2324,6 +2234,11 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Barrträd</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2337,6 +2252,341 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>112209144</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Storberget sydväst, Storberget sydväst, Mpd</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>623207</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6933474</v>
+      </c>
+      <c r="S16" t="n">
+        <v>15</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2023-09-18</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>18:51</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2023-09-18</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>18:51</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Barrträd</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Fredrik Schaerström</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Fredrik Schaerström</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>112061062</v>
+      </c>
+      <c r="B17" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Storberget sydväst, Storberget sydväst, Mpd</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>623215</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6933489</v>
+      </c>
+      <c r="S17" t="n">
+        <v>20</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2023-09-11</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2023-09-11</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Fredrik Schaerström</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Fredrik Schaerström</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>133769545</v>
+      </c>
+      <c r="B18" t="n">
+        <v>104707</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Storberget, Storberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>623223</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6933548</v>
+      </c>
+      <c r="S18" t="n">
+        <v>15</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Fredrik Schaerström</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Fredrik Schaerström</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 24538-2023 artfynd.xlsx
+++ b/artfynd/A 24538-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112061032</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -897,6 +907,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112209570</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1004,6 +1019,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112209075</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1111,6 +1131,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112209081</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1228,6 +1253,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112061235</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1335,6 +1365,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112061330</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1442,6 +1477,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112061132</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1553,6 +1593,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111926752</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1664,6 +1709,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112061086</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1775,6 +1825,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112061096</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1886,6 +1941,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112061114</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2008,6 +2068,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112209105</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2130,6 +2195,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112209118</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2252,6 +2322,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112209136</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2374,6 +2449,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112209144</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2481,6 +2561,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112061062</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2587,8 +2672,32 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133769545</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>